--- a/02_Spielerliste.xlsx
+++ b/02_Spielerliste.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roland.Koll.SAR-ET\OneDrive - SAR Anlagenbau GmbH\Dokumente\Stocksport\Aktuell\Stocksport_Dashboard_V2.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saranlagen-my.sharepoint.com/personal/roland_koll_sar-anlagenbau_at/Documents/Dokumente/Stocksport/Aktuell/Stocksport_Dashboard_V2.5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F40131-A1EA-4ACD-BC92-0B7F6E4BCB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{85F40131-A1EA-4ACD-BC92-0B7F6E4BCB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02741C9F-A92D-4F4C-AEE5-64926F3F53A9}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="1560" windowWidth="29010" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spieler" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="56">
   <si>
     <t>Spieler-ID</t>
   </si>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -662,7 +662,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -673,7 +673,7 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -684,7 +684,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -706,7 +706,7 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -851,6 +851,9 @@
       <c r="B24" t="s">
         <v>52</v>
       </c>
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -859,6 +862,9 @@
       <c r="B25" t="s">
         <v>53</v>
       </c>
+      <c r="C25" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -867,6 +873,9 @@
       <c r="B26" t="s">
         <v>54</v>
       </c>
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -874,13 +883,16 @@
       </c>
       <c r="B27" t="s">
         <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C5 A9:C9 A6 A7 A8 A10" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C5 A9 A6 A7 A8 A10 C9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>